--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484736_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484736_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.605700000000001</v>
+        <v>7.707</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0483</v>
+        <v>6.6787</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5574</v>
+        <v>1.0283</v>
       </c>
       <c r="G2" t="n">
         <v>3.7283</v>
@@ -610,13 +610,13 @@
         <v>0.7548</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4625</v>
+        <v>1.5639</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4196</v>
+        <v>1.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0429</v>
+        <v>0.5139</v>
       </c>
       <c r="V2" t="n">
         <v>2.7922</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0001</v>
+        <v>6.442</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2142</v>
+        <v>6.6296</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2141</v>
+        <v>-0.1876</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8233</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>1.258</v>
+        <v>0.6998</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4319</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.174</v>
+        <v>-0.1475</v>
       </c>
       <c r="V3" t="n">
         <v>6.188</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3589</v>
+        <v>6.3366</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4388</v>
+        <v>5.6282</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9201</v>
+        <v>0.7085</v>
       </c>
       <c r="G4" t="n">
         <v>5.5153</v>
@@ -766,13 +766,13 @@
         <v>0.9435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0324</v>
+        <v>1.0101</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4115</v>
+        <v>0.7778</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4439</v>
+        <v>0.2323</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6516</v>
+        <v>4.9028</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5889</v>
+        <v>2.9988</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0627</v>
+        <v>1.904</v>
       </c>
       <c r="G5" t="n">
         <v>2.8487</v>
@@ -844,13 +844,13 @@
         <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2934</v>
+        <v>0.5445</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2039</v>
+        <v>0.6138</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.0693</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>M. ISIDRO PENA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0391</v>
+        <v>2.4407</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7032</v>
+        <v>1.6905</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6641</v>
+        <v>0.7502</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6318</v>
+        <v>0.2575</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.306</v>
+        <v>-0.3921</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9378</v>
+        <v>0.6496</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6156</v>
+        <v>0.0634</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5643</v>
+        <v>0.0634</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1799</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0162</v>
+        <v>0.1941</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2583</v>
+        <v>-0.4555</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7579</v>
+        <v>0.6496</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3132</v>
+        <v>0.1833</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2579</v>
+        <v>0.3819</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0553</v>
+        <v>-0.1987</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.585</v>
+        <v>1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9054</v>
+        <v>1.2452</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ISIDRO PENA</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8154</v>
+        <v>2.1775</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1446</v>
+        <v>2.4849</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6709000000000001</v>
+        <v>-0.3075</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2575</v>
+        <v>1.2997</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3921</v>
+        <v>0.1761</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6496</v>
+        <v>1.1236</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0634</v>
+        <v>1.1115</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0634</v>
+        <v>0.486</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1941</v>
+        <v>0.1882</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4555</v>
+        <v>-0.3099</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6496</v>
+        <v>0.4981</v>
       </c>
       <c r="P7" t="n">
         <v>0.7548</v>
@@ -1000,28 +1000,28 @@
         <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4421</v>
+        <v>0.123</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.164</v>
+        <v>0.1283</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.278</v>
+        <v>-0.0053</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5295</v>
+        <v>1.1521</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0751</v>
+        <v>1.7103</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5456</v>
+        <v>-0.5583</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2997</v>
+        <v>2.6318</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1761</v>
+        <v>-0.306</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1236</v>
+        <v>2.9378</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1115</v>
+        <v>1.6156</v>
       </c>
       <c r="K8" t="n">
-        <v>0.486</v>
+        <v>-0.5643</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6254999999999999</v>
+        <v>2.1799</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1882</v>
+        <v>1.0162</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3099</v>
+        <v>0.2583</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4981</v>
+        <v>0.7579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7548</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R8" t="n">
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5249</v>
+        <v>1.4261</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2816</v>
+        <v>1.265</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2433</v>
+        <v>0.1611</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.585</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2452</v>
+        <v>0.9054</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ISIDRO PEÑA</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.317</v>
+        <v>0.6347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.317</v>
+        <v>-0.4771</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.1118</v>
       </c>
       <c r="G9" t="n">
-        <v>0.317</v>
+        <v>0.0693</v>
       </c>
       <c r="H9" t="n">
-        <v>0.317</v>
+        <v>-0.8812</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.9505</v>
       </c>
       <c r="J9" t="n">
-        <v>0.317</v>
+        <v>-0.4817</v>
       </c>
       <c r="K9" t="n">
-        <v>0.317</v>
+        <v>-0.5228</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.3584</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.9094</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.0045</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.0053</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>M. ISIDRO PEÑA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2404</v>
+        <v>0.317</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6333</v>
+        <v>0.317</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8737</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0693</v>
+        <v>0.317</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8812</v>
+        <v>0.317</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9505</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4817</v>
+        <v>0.317</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5228</v>
+        <v>0.317</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3584</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9094</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.395</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1517</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2433</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7739</v>
+        <v>-1.1063</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5219</v>
+        <v>-2.4937</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2957</v>
+        <v>1.3874</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8735</v>
+        <v>-0.4628</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7239</v>
+        <v>-0.2285</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1496</v>
+        <v>-0.2343</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0772</v>
+        <v>-0.851</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.4226</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4354</v>
+        <v>-1.2736</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9507</v>
+        <v>0.3882</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2365</v>
+        <v>-0.6511</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7143</v>
+        <v>1.0393</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0757</v>
+        <v>-1.887</v>
       </c>
       <c r="R11" t="n">
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9111</v>
+        <v>-0.0209</v>
       </c>
       <c r="T11" t="n">
-        <v>1.596</v>
+        <v>0.2442</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3151</v>
+        <v>-0.2651</v>
       </c>
       <c r="V11" t="n">
         <v>0.3208</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6036</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8232</v>
+        <v>-1.2047</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0783</v>
+        <v>0.2497</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2551</v>
+        <v>-1.4544</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4628</v>
+        <v>-1.8735</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2285</v>
+        <v>-0.7239</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2343</v>
+        <v>-1.1496</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.851</v>
+        <v>0.0772</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4226</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2736</v>
+        <v>-0.4354</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3882</v>
+        <v>-1.9507</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6511</v>
+        <v>-1.2365</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0393</v>
+        <v>-0.7143</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R12" t="n">
         <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7377</v>
+        <v>1.4802</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3404</v>
+        <v>1.3238</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3974</v>
+        <v>0.1564</v>
       </c>
       <c r="V12" t="n">
         <v>0.3208</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3208</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.503</v>
+        <v>-3.4597</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4069</v>
+        <v>-2.6018</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0961</v>
+        <v>-0.858</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7401</v>
@@ -1468,13 +1468,13 @@
         <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7277</v>
+        <v>0.7709</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1968</v>
+        <v>1.0019</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4691</v>
+        <v>-0.231</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6036</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.4576</v>
+        <v>26.3397</v>
       </c>
       <c r="E14" t="n">
-        <v>21.9335</v>
+        <v>22.8151</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5243</v>
+        <v>3.5244</v>
       </c>
       <c r="G14" t="n">
         <v>11.7679</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07819999999999983</v>
+        <v>0.07819999999999971</v>
       </c>
       <c r="I14" t="n">
         <v>11.6895</v>
@@ -1546,13 +1546,13 @@
         <v>10.3785</v>
       </c>
       <c r="S14" t="n">
-        <v>6.8986</v>
+        <v>7.7802</v>
       </c>
       <c r="T14" t="n">
-        <v>6.7569</v>
+        <v>7.638500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1415000000000002</v>
+        <v>0.1415</v>
       </c>
       <c r="V14" t="n">
         <v>8.6784</v>
@@ -1561,7 +1561,7 @@
         <v>13.3004</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.622</v>
+        <v>-4.622000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2628</v>
+        <v>1.5959</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2659</v>
+        <v>3.3633</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0031</v>
+        <v>-1.7674</v>
       </c>
       <c r="G15" t="n">
         <v>0.5007</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8606</v>
+        <v>-0.5275</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1023</v>
+        <v>-0.0049</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7583</v>
+        <v>-0.5225</v>
       </c>
       <c r="V15" t="n">
         <v>0.3018</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>J. NAVARRO MORALES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2193</v>
+        <v>0.0573</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6051</v>
+        <v>1.4068</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8244</v>
+        <v>-1.3495</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.268</v>
+        <v>1.3818</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.1088</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9762</v>
+        <v>1.273</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7533</v>
+        <v>2.1246</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9291</v>
+        <v>0.8084</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1757</v>
+        <v>1.3162</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0213</v>
+        <v>-0.7428</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2208</v>
+        <v>-0.6996</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8005</v>
+        <v>-0.0431</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1887</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2374</v>
+        <v>-0.0417</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4936</v>
+        <v>0.2257</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2562</v>
+        <v>-0.2674</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.9054</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2452</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. NAVARRO MORALES</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3854</v>
+        <v>-1.3925</v>
       </c>
       <c r="E17" t="n">
-        <v>1.017</v>
+        <v>-0.8893</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4024</v>
+        <v>-0.5031</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3818</v>
+        <v>-0.4098</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1088</v>
+        <v>0.4148</v>
       </c>
       <c r="I17" t="n">
-        <v>1.273</v>
+        <v>-0.8246</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1246</v>
+        <v>0.9129</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8084</v>
+        <v>1.5214</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3162</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7428</v>
+        <v>-1.3227</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6996</v>
+        <v>-1.1066</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0431</v>
+        <v>-0.2162</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4844</v>
+        <v>-0.379</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.164</v>
+        <v>0.0847</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3204</v>
+        <v>-0.4638</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9054</v>
+        <v>-0.6036</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9054</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>M. PEREZ MARCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5549</v>
+        <v>-1.4538</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7919</v>
+        <v>-0.5713</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7629</v>
+        <v>-0.8825</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4098</v>
+        <v>-1.6138</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4148</v>
+        <v>-0.2716</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8246</v>
+        <v>-1.3422</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9129</v>
+        <v>-0.6284</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5214</v>
+        <v>0.0211</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6496</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3227</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1066</v>
+        <v>-0.2927</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2162</v>
+        <v>-0.6927</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.887</v>
+        <v>0.1887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5414</v>
+        <v>-0.0287</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1822</v>
+        <v>0.0572</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7236</v>
+        <v>-0.0858</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>O. TALENS ALBERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6334</v>
+        <v>-1.4683</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7265</v>
+        <v>-1.5079</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3599</v>
+        <v>0.0396</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3855</v>
+        <v>-1.3247</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2124</v>
+        <v>-0.4805</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.5979</v>
+        <v>-0.8442</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5588</v>
+        <v>-0.5118</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4252</v>
+        <v>0.1377</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8664</v>
+        <v>-0.6496</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9443</v>
+        <v>-0.8128</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2128</v>
+        <v>-0.6182</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7315</v>
+        <v>-0.1946</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.6341</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4884</v>
+        <v>-0.3544</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1139</v>
+        <v>-0.2798</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9434</v>
+        <v>0.3018</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3208</v>
+        <v>0.3018</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. PEREZ MARCO</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7725</v>
+        <v>-1.8851</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8636</v>
+        <v>0.3385</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.909</v>
+        <v>-2.2236</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6138</v>
+        <v>-1.268</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2716</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3422</v>
+        <v>-1.9762</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6284</v>
+        <v>0.7533</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0211</v>
+        <v>1.9291</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6496</v>
+        <v>-1.1757</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-2.0213</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2927</v>
+        <v>-1.2208</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6927</v>
+        <v>-0.8005</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3474</v>
+        <v>-0.4284</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2352</v>
+        <v>0.227</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1123</v>
+        <v>-0.6554</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. TALENS ALBERO</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8135</v>
+        <v>-1.9221</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8002</v>
+        <v>0.3367</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0133</v>
+        <v>-2.2588</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3247</v>
+        <v>-1.3855</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4805</v>
+        <v>2.2124</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8442</v>
+        <v>-3.5979</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5118</v>
+        <v>0.5588</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1377</v>
+        <v>2.4252</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6496</v>
+        <v>-1.8664</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8128</v>
+        <v>-1.9443</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6182</v>
+        <v>-0.2128</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1946</v>
+        <v>-1.7315</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9794</v>
+        <v>-0.9141</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.0987</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3327</v>
+        <v>-1.0128</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3018</v>
+        <v>-0.9434</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3018</v>
+        <v>-0.3208</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2078</v>
+        <v>-2.1224</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0679</v>
+        <v>0.9705</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2757</v>
+        <v>-3.0929</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0415</v>
@@ -2170,13 +2170,13 @@
         <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.7982</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0029</v>
+        <v>-0.0945</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8864</v>
+        <v>-0.7036</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2262</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8265</v>
+        <v>-2.5523</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7923</v>
+        <v>-0.5974</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0342</v>
+        <v>-1.9548</v>
       </c>
       <c r="G23" t="n">
         <v>-0.441</v>
@@ -2248,13 +2248,13 @@
         <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2534</v>
+        <v>0.0209</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2352</v>
+        <v>-0.0403</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0182</v>
+        <v>0.0611</v>
       </c>
       <c r="V23" t="n">
         <v>-1.566</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2047</v>
+        <v>-5.2461</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9104</v>
+        <v>-0.4232</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.2943</v>
+        <v>-4.8229</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6666</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9346</v>
+        <v>-0.976</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5755</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3591</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7922</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.1023</v>
+        <v>-7.7692</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.0485</v>
+        <v>-5.9511</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0538</v>
+        <v>-1.8181</v>
       </c>
       <c r="G25" t="n">
         <v>-4.4993</v>
@@ -2404,13 +2404,13 @@
         <v>1.6983</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2257</v>
+        <v>-0.8925</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3498</v>
+        <v>-0.2524</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8759</v>
+        <v>-0.6401</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2452</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-25.4575</v>
+        <v>-24.1586</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.5245</v>
+        <v>-3.5244</v>
       </c>
       <c r="F26" t="n">
-        <v>-21.933</v>
+        <v>-20.634</v>
       </c>
       <c r="G26" t="n">
         <v>-11.7677</v>
@@ -2470,7 +2470,7 @@
         <v>-7.3249</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.816500000000001</v>
+        <v>-6.8165</v>
       </c>
       <c r="P26" t="n">
         <v>1.887</v>
@@ -2482,13 +2482,13 @@
         <v>12.2655</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.8986</v>
+        <v>-5.599299999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1416000000000001</v>
+        <v>-0.1416</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.757</v>
+        <v>-5.457700000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-8.6784</v>
